--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892A95-BBDD-42B6-A9C8-E869A5FA9CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190519FC-56E1-4778-9210-A8FD9EFB27E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4660" windowWidth="40520" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,38 @@
   </si>
   <si>
     <t>字段变体</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多语言表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>多语言Key</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbLocalzationKeyData</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -177,7 +209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -186,6 +218,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -467,17 +505,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
+    <col min="2" max="4" width="20.58203125" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
     <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,17 +544,17 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,11 +580,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E3" t="s">
@@ -568,6 +607,37 @@
       </c>
       <c r="P3" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190519FC-56E1-4778-9210-A8FD9EFB27E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21535636-D68C-4D6F-8EF1-CB2835F2F5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4660" windowWidth="40520" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="5250" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -124,6 +124,94 @@
   </si>
   <si>
     <t>TbLocalzationKeyData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbUlocakPropData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求数量(大于等于)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbUlocakItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求的物品ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求的物品数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbCharacterData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色属性类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbDateData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeFlag</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -169,7 +257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -188,6 +276,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -209,7 +315,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -227,6 +333,33 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -505,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="20.58203125" customWidth="1"/>
@@ -513,7 +646,7 @@
     <col min="7" max="9" width="15" customWidth="1"/>
     <col min="10" max="12" width="13.5" customWidth="1"/>
     <col min="13" max="13" width="10.33203125" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -602,7 +735,7 @@
       <c r="M3" t="s">
         <v>17</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -622,7 +755,7 @@
       <c r="L4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -636,8 +769,184 @@
       <c r="L5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="9"/>
+      <c r="N8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="9"/>
+      <c r="N9" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B10" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M10" s="11"/>
+      <c r="N10" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="11"/>
+      <c r="N12" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21535636-D68C-4D6F-8EF1-CB2835F2F5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E03F621-831B-4536-9DFD-C12476674F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="5250" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="63680" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -131,10 +131,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>PropID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>属性ID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -171,10 +167,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>TbCharacterData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>CharacterID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -195,10 +187,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>TbDateData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>long</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -212,6 +200,48 @@
   </si>
   <si>
     <t>需求时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbUlockCharacterData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbUlockDateData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeekFlag</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求周</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowRuleTimeType</t>
+  </si>
+  <si>
+    <t>ShowRuleWeekType</t>
+  </si>
+  <si>
+    <t>周几</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间段</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterPropType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -219,7 +249,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,8 +286,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,6 +330,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39991454817346722"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -315,7 +375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -331,9 +391,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -355,11 +412,32 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -638,13 +716,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="20.58203125" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="18.9140625" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" style="4" customWidth="1"/>
     <col min="13" max="13" width="10.33203125" customWidth="1"/>
     <col min="14" max="14" width="20.33203125" customWidth="1"/>
   </cols>
@@ -677,15 +757,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -697,7 +777,7 @@
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="M2" t="s">
@@ -729,7 +809,7 @@
       <c r="K3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="M3" t="s">
@@ -752,7 +832,7 @@
       <c r="K4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="N4" s="3" t="s">
@@ -766,187 +846,217 @@
       <c r="K5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="6" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="L6" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="6"/>
+      <c r="N6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L7" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9" s="8"/>
+      <c r="N9" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12" s="10"/>
+      <c r="N12" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="J14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B10" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="11"/>
-      <c r="N12" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>52</v>
+      <c r="L14" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E03F621-831B-4536-9DFD-C12476674F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D085322C-A998-4558-88C9-784E3AB42E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="63680" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1220" yWindow="1160" windowWidth="33700" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -242,6 +242,78 @@
   </si>
   <si>
     <t>CharacterPropType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remark</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NameKey</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DescKey</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯一ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称多语言</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述多语言</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆叠上限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxNumber</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quality</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IconName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标名称</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbItem</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -249,7 +321,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,8 +364,23 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2329"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,8 +441,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -363,6 +456,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -375,7 +483,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -418,25 +526,43 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -716,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="20.58203125" customWidth="1"/>
@@ -757,15 +883,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -870,7 +996,7 @@
       <c r="K6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="14" t="s">
         <v>53</v>
       </c>
       <c r="M6" s="6"/>
@@ -893,7 +1019,7 @@
       <c r="K7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="15" t="s">
         <v>47</v>
       </c>
       <c r="M7" s="6"/>
@@ -918,7 +1044,7 @@
       <c r="K8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="L8" s="16" t="s">
         <v>46</v>
       </c>
       <c r="M8" s="8"/>
@@ -941,7 +1067,7 @@
       <c r="K9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="L9" s="16" t="s">
         <v>47</v>
       </c>
       <c r="M9" s="8"/>
@@ -966,7 +1092,7 @@
       <c r="K10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="17" t="s">
         <v>46</v>
       </c>
       <c r="M10" s="10"/>
@@ -989,7 +1115,7 @@
       <c r="K11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="17" t="s">
         <v>60</v>
       </c>
       <c r="M11" s="10"/>
@@ -1012,7 +1138,7 @@
       <c r="K12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="18" t="s">
+      <c r="L12" s="17" t="s">
         <v>47</v>
       </c>
       <c r="M12" s="10"/>
@@ -1037,7 +1163,7 @@
       <c r="K13" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="18" t="s">
         <v>57</v>
       </c>
       <c r="M13" s="13"/>
@@ -1052,11 +1178,197 @@
       <c r="K14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="20" t="s">
+      <c r="L14" s="19" t="s">
         <v>56</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="M15" s="22"/>
+      <c r="N15" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="22"/>
+      <c r="N16" s="24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="22"/>
+      <c r="N17" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="K18" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="22"/>
+      <c r="N18" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="22"/>
+      <c r="N20" s="25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="M21" s="22"/>
+      <c r="N21" s="25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="25" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D085322C-A998-4558-88C9-784E3AB42E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="1160" windowWidth="33700" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5850" yWindow="950" windowWidth="28250" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -483,7 +483,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -544,9 +544,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -556,13 +553,13 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -883,15 +880,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1186,188 +1183,188 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="21" t="s">
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="K15" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="L15" s="21" t="s">
+      <c r="L15" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="22"/>
-      <c r="N15" s="23" t="s">
+      <c r="M15" s="21"/>
+      <c r="N15" s="22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="21"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="21" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="L16" s="21" t="s">
+      <c r="L16" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="M16" s="22"/>
-      <c r="N16" s="24" t="s">
+      <c r="M16" s="21"/>
+      <c r="N16" s="23" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="21" t="s">
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="21" t="s">
+      <c r="K17" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="21" t="s">
+      <c r="L17" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="M17" s="22"/>
-      <c r="N17" s="21" t="s">
+      <c r="M17" s="21"/>
+      <c r="N17" s="20" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="21" t="s">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="K18" s="21" t="s">
+      <c r="K18" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="L18" s="21" t="s">
+      <c r="L18" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="M18" s="22"/>
-      <c r="N18" s="21" t="s">
+      <c r="M18" s="21"/>
+      <c r="N18" s="20" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="21" t="s">
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="25" t="s">
+      <c r="K19" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="L19" s="21" t="s">
+      <c r="L19" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="M19" s="22"/>
-      <c r="N19" s="25" t="s">
+      <c r="M19" s="21"/>
+      <c r="N19" s="20" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="21" t="s">
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="K20" s="25" t="s">
+      <c r="K20" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="L20" s="26" t="s">
+      <c r="L20" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="M20" s="22"/>
-      <c r="N20" s="25" t="s">
+      <c r="M20" s="21"/>
+      <c r="N20" s="20" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="21" t="s">
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="K21" s="25" t="s">
+      <c r="K21" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="L21" s="21" t="s">
+      <c r="L21" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="M21" s="22"/>
-      <c r="N21" s="25" t="s">
+      <c r="M21" s="21"/>
+      <c r="N21" s="20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="21" t="s">
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="K22" s="25" t="s">
+      <c r="K22" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="L22" s="26" t="s">
+      <c r="L22" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="M22" s="22"/>
-      <c r="N22" s="25" t="s">
+      <c r="M22" s="21"/>
+      <c r="N22" s="20" t="s">
         <v>74</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D085322C-A998-4558-88C9-784E3AB42E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E17A34-1A86-49FE-8DBF-079B170D8FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="950" windowWidth="28250" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5550" yWindow="1660" windowWidth="30220" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -242,78 +242,6 @@
   </si>
   <si>
     <t>CharacterPropType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remark</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NameKey</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DescKey</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>唯一ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>名称多语言</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述多语言</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>堆叠上限</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxNumber</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Quality</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>品质</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IconName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>图标名称</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemQuality</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbItem</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -321,7 +249,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,23 +292,8 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1F2329"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,14 +354,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -456,21 +363,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFDEE0E3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -483,7 +375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -542,21 +434,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
@@ -839,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="20.58203125" customWidth="1"/>
@@ -880,15 +757,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1182,192 +1059,6 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B15" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="L15" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" s="21"/>
-      <c r="N15" s="22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="L16" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" s="21"/>
-      <c r="N16" s="23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="K17" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="L17" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="21"/>
-      <c r="N17" s="20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="L18" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="21"/>
-      <c r="N18" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" s="21"/>
-      <c r="N19" s="20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="L20" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="M20" s="21"/>
-      <c r="N20" s="20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="K21" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="L21" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="M21" s="21"/>
-      <c r="N21" s="20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="K22" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="M22" s="21"/>
-      <c r="N22" s="20" t="s">
-        <v>74</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E17A34-1A86-49FE-8DBF-079B170D8FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC47111-153B-40FD-8137-D8B2BB52EBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5550" yWindow="1660" windowWidth="30220" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="30220" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -242,6 +242,40 @@
   </si>
   <si>
     <t>CharacterPropType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbRewardItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbRewardPropData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">PropType </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyType</t>
+  </si>
+  <si>
+    <t>属性类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbRewardCharacterPropData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterPropType</t>
+  </si>
+  <si>
+    <t>角色好感数值</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -249,7 +283,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,8 +326,15 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,6 +395,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -375,7 +428,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -438,6 +491,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -716,10 +790,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="20.58203125" customWidth="1"/>
+    <col min="2" max="2" width="26.4140625" customWidth="1"/>
+    <col min="3" max="4" width="20.58203125" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
@@ -1059,6 +1134,126 @@
         <v>59</v>
       </c>
     </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC47111-153B-40FD-8137-D8B2BB52EBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0A9792-17C4-4E1C-AE79-83C3A1A0DF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="30220" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5060" yWindow="1980" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -489,9 +489,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -512,6 +509,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -832,15 +832,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1175,82 +1175,82 @@
       </c>
     </row>
     <row r="17" spans="2:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="24" t="s">
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="K17" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="L17" s="26" t="s">
+      <c r="L17" s="25" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="24" t="s">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="K18" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="24" t="s">
+      <c r="L18" s="23" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="27" t="s">
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="K19" s="23" t="s">
+      <c r="K19" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="L19" s="27" t="s">
+      <c r="L19" s="26" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="21" t="s">
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="21" t="s">
+      <c r="K20" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="21" t="s">
+      <c r="L20" s="20" t="s">
         <v>47</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0A9792-17C4-4E1C-AE79-83C3A1A0DF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC6AFC8-16AE-46C3-BADC-A3CA18726665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="1980" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60795" yWindow="6390" windowWidth="30585" windowHeight="18375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -790,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.4140625" customWidth="1"/>
@@ -1236,7 +1236,7 @@
       </c>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="21"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
@@ -1244,13 +1244,32 @@
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
       <c r="I20" s="21"/>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K21" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="20" t="s">
+      <c r="L21" s="20" t="s">
         <v>47</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC6AFC8-16AE-46C3-BADC-A3CA18726665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0D5059-72C9-4D76-9200-A5C06ED7F907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60795" yWindow="6390" windowWidth="30585" windowHeight="18375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5020" yWindow="1450" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -276,6 +276,30 @@
   </si>
   <si>
     <t>角色好感数值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbPopularityData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>排名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字多语言</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人气数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -334,7 +358,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,6 +431,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -428,7 +458,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -512,6 +542,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -790,7 +826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.4140625" customWidth="1"/>
@@ -1273,6 +1309,65 @@
         <v>47</v>
       </c>
     </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="K22" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="K23" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="L24" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0D5059-72C9-4D76-9200-A5C06ED7F907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2F2DA4-364A-45BF-B256-FF7955E1759D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5020" yWindow="1450" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5360" yWindow="1790" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -276,30 +276,6 @@
   </si>
   <si>
     <t>角色好感数值</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbPopularityData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>排名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>名字多语言</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人气数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -540,14 +516,14 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -868,15 +844,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1310,63 +1286,43 @@
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="K22" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="L22" s="28" t="s">
-        <v>47</v>
-      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="K23" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="L23" s="28" t="s">
-        <v>30</v>
-      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>47</v>
-      </c>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2F2DA4-364A-45BF-B256-FF7955E1759D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58488A2-ED30-43A5-ABFC-BA5A0DB3418E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5360" yWindow="1790" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -276,6 +276,10 @@
   </si>
   <si>
     <t>角色好感数值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbConsumption</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1186,7 +1190,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B17" s="23" t="s">
         <v>62</v>
       </c>
@@ -1207,7 +1211,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="24"/>
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
@@ -1226,7 +1230,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
         <v>67</v>
       </c>
@@ -1247,7 +1251,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="22"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
@@ -1266,7 +1270,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
@@ -1285,8 +1289,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="27"/>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="27" t="s">
+        <v>70</v>
+      </c>
       <c r="C22" s="28"/>
       <c r="D22" s="28"/>
       <c r="E22" s="28"/>
@@ -1294,11 +1300,20 @@
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
       <c r="I22" s="28"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="J22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
@@ -1307,11 +1322,20 @@
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
       <c r="I23" s="28"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="J23" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
